--- a/data/fsa/2026_ARC_CO.xlsx
+++ b/data/fsa/2026_ARC_CO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-0911\Program Year 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-1009\Program Year 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1155DB6C-540F-4690-96AA-F28B8EACE8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1BF62F-D218-4311-BBC2-B57BA9FE3D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>BASED ON 2020/21-2024/25 MARKET YEAR AVERAGE (MYA) PRICES, 2026 EFFECTIVE REFERENCE PRICES AND 2026 NATIONAL LOAN RATES</t>
   </si>
   <si>
-    <t>September 11, 2026 1/</t>
+    <t>October 9, 2026 1/</t>
   </si>
   <si>
     <t>Commodity</t>
@@ -1069,7 +1069,7 @@
         <v>6.98</v>
       </c>
       <c r="L9" s="4">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>21</v>
@@ -1078,7 +1078,7 @@
         <v>3.72</v>
       </c>
       <c r="O9" s="4">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>21</v>
@@ -1269,7 +1269,7 @@
         <v>5.03</v>
       </c>
       <c r="L13" s="4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>21</v>
@@ -1278,7 +1278,7 @@
         <v>2.42</v>
       </c>
       <c r="O13" s="4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>21</v>
@@ -1319,7 +1319,7 @@
         <v>5.3</v>
       </c>
       <c r="L14" s="4">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>21</v>
@@ -1328,7 +1328,7 @@
         <v>2.42</v>
       </c>
       <c r="O14" s="4">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>21</v>
@@ -1419,7 +1419,7 @@
         <v>0.14929999999999999</v>
       </c>
       <c r="L16" s="12">
-        <v>0.112</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>21</v>
@@ -1428,7 +1428,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
       <c r="O16" s="12">
-        <v>0.112</v>
+        <v>9.4E-2</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>21</v>
@@ -1469,7 +1469,7 @@
         <v>0.35299999999999998</v>
       </c>
       <c r="L17" s="12">
-        <v>0.17</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>21</v>
@@ -1478,7 +1478,7 @@
         <v>0.14299999999999999</v>
       </c>
       <c r="O17" s="12">
-        <v>0.17</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>21</v>
@@ -1519,7 +1519,7 @@
         <v>0.25950000000000001</v>
       </c>
       <c r="L18" s="12">
-        <v>0.245</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>21</v>
@@ -1528,7 +1528,7 @@
         <v>0.111</v>
       </c>
       <c r="O18" s="12">
-        <v>0.245</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>21</v>
@@ -1569,7 +1569,7 @@
         <v>0.35470000000000002</v>
       </c>
       <c r="L19" s="12">
-        <v>0.21</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>21</v>
@@ -1578,7 +1578,7 @@
         <v>0.154</v>
       </c>
       <c r="O19" s="12">
-        <v>0.21</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>21</v>
@@ -1619,7 +1619,7 @@
         <v>0.30680000000000002</v>
       </c>
       <c r="L20" s="12">
-        <v>0.16700000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>21</v>
@@ -1628,7 +1628,7 @@
         <v>0.11</v>
       </c>
       <c r="O20" s="12">
-        <v>0.16700000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>21</v>
@@ -1669,7 +1669,7 @@
         <v>0.25119999999999998</v>
       </c>
       <c r="L21" s="12">
-        <v>0.247</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>21</v>
@@ -1678,7 +1678,7 @@
         <v>0.111</v>
       </c>
       <c r="O21" s="12">
-        <v>0.247</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>21</v>
@@ -1719,7 +1719,7 @@
         <v>14.7</v>
       </c>
       <c r="L22" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>21</v>
@@ -1728,7 +1728,7 @@
         <v>6.2160000000000002</v>
       </c>
       <c r="O22" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>21</v>
@@ -1769,7 +1769,7 @@
         <v>0.39369999999999999</v>
       </c>
       <c r="L23" s="12">
-        <v>0.317</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>21</v>
@@ -1778,7 +1778,7 @@
         <v>0.111</v>
       </c>
       <c r="O23" s="12">
-        <v>0.317</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>21</v>
@@ -1869,7 +1869,7 @@
         <v>0.27729999999999999</v>
       </c>
       <c r="L25" s="12">
-        <v>0.215</v>
+        <v>0.22750000000000001</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>21</v>
@@ -1878,7 +1878,7 @@
         <v>0.111</v>
       </c>
       <c r="O25" s="12">
-        <v>0.215</v>
+        <v>0.22750000000000001</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>21</v>
@@ -2019,7 +2019,7 @@
         <v>0.43109999999999998</v>
       </c>
       <c r="L28" s="12">
-        <v>0.41139999999999999</v>
+        <v>0.41470000000000001</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>21</v>
@@ -2028,7 +2028,7 @@
         <v>0.3</v>
       </c>
       <c r="O28" s="12">
-        <v>0.41139999999999999</v>
+        <v>0.41470000000000001</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>21</v>
@@ -2069,7 +2069,7 @@
         <v>0.16900000000000001</v>
       </c>
       <c r="L29" s="12">
-        <v>0.13500000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>21</v>
@@ -2078,7 +2078,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="O29" s="12">
-        <v>0.13500000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>21</v>
@@ -2362,6 +2362,6 @@
     <mergeCell ref="K6:K7"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="1.6" header="0" footer="0"/>
-  <pageSetup scale="69" orientation="landscape" cellComments="atEnd" horizontalDpi="2400" verticalDpi="2400" r:id="rId1"/>
+  <pageSetup scale="69" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>